--- a/sources/jin_step7.xlsx
+++ b/sources/jin_step7.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA138"/>
+  <dimension ref="A1:AB138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="59" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="157" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>1fc23c0d-27d6-4421-ae04-82e296cfe349</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>846c1d82-acd7-471d-a898-6519f622274a</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0376c747-3555-4bcd-a34b-40834f2b731b</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>1bba05e3-1125-4b29-9190-3335d5e3e198</t>
         </is>
@@ -730,22 +736,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f,f+1+2 [~5]</t>
+          <t>f,f+1+2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f,f+1+2 [~5]</t>
+          <t>f,f+1+2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stone Head - [Tag]</t>
+          <t>Stone Head -</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stone Head - [Tag]</t>
+          <t>Stone Head -</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -790,10 +796,15 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>6c991783-0346-4871-bf41-7746cc045080</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>13d40c7e-6854-454c-8bf9-a45114c252dc</t>
         </is>
@@ -855,12 +866,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>7163c970-ac14-4802-bd65-2eede14a895e</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>81ac5bc6-daac-4ef9-9c20-a996a21953e5</t>
         </is>
@@ -922,12 +933,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>979632c7-e5b6-48a3-be68-3f5d10e4cda3</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>ec1af669-5e82-4d16-ab19-60f60b48d325</t>
         </is>
@@ -984,12 +995,12 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1036,17 +1047,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1093,17 +1104,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1150,17 +1161,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1207,17 +1218,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1264,17 +1275,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1331,12 +1342,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1393,12 +1404,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1455,12 +1466,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1592,20 +1603,25 @@
       </c>
       <c r="X19" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y19" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y19" s="1" t="inlineStr">
+      <c r="Z19" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z19" s="1" t="inlineStr">
+      <c r="AA19" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA19" s="1" t="inlineStr">
+      <c r="AB19" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1687,12 +1703,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>342c72d2-bcf6-41ff-93b3-455cba39507d</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>85ef1f81-b5b3-415e-9bae-fcad79bbba56</t>
         </is>
@@ -1774,12 +1790,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>eee61db1-ffb0-42cd-9d84-01ffa73217e7</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>a81778f7-ae79-41ab-937d-b95437a297ee</t>
         </is>
@@ -1861,12 +1877,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>107f9188-73d0-4ab3-a46c-c694465fc4cf</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>9fa3928f-0448-4225-b081-6487d519a269</t>
         </is>
@@ -1948,12 +1964,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>8310c13f-2a53-439d-84a6-e21d2adbfe3d</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>c0642b21-4f24-47e8-8de1-798b9b20189f</t>
         </is>
@@ -2035,12 +2051,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>952aeaec-c71e-490e-ac17-2449ef159c81</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>a5461e92-5b34-418d-b398-b0ac4a30f19e</t>
         </is>
@@ -2122,12 +2138,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>2c380826-9f48-4ce3-9225-1a6e5777b005</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>b293d99a-188d-4448-b593-b10a475b3bd5</t>
         </is>
@@ -2209,12 +2225,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>bcc8a48a-d690-483a-9dc9-6a3295d64398</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>571826af-3182-403f-989f-d9e5273324ad</t>
         </is>
@@ -2296,12 +2312,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>638cfdf7-83a7-4a97-b6e5-bbeaa8743669</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>964a3fcd-2c30-4c0f-8014-08b4010f7e0d</t>
         </is>
@@ -2383,12 +2399,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>6b5b01ce-c27c-4cd0-87d9-0949033451c3</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>98fb20b7-b139-4845-b6e4-055dd57fbc55</t>
         </is>
@@ -2470,12 +2486,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>f2d3fc36-2331-4f8f-8003-29e811f05736</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>a262030f-def1-42cb-9355-385cc8ada115</t>
         </is>
@@ -2557,12 +2573,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>7715ee82-1244-4873-bac1-be236455f34c</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>c2c87c8c-b859-490e-a4db-481ba37cac07</t>
         </is>
@@ -2644,12 +2660,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>77a42648-ab94-40c2-b72f-0be90d3cc446</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>b96b2e61-3a45-418c-a2d0-53160a54e19f</t>
         </is>
@@ -2731,12 +2747,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>8fb641c2-77cf-4f70-ad6d-7fa410ff43b4</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>8618a665-283b-4c18-8ed4-3bdedb71f083</t>
         </is>
@@ -2818,12 +2834,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>bbe99fd2-88df-4114-9b23-cbbe06d553f8</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>8f89af65-9f24-4425-8445-77193a60c4d0</t>
         </is>
@@ -2905,12 +2921,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>216a966a-76ec-48dc-990d-386d3ec44b3e</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>a01b0e46-5cfb-421e-88d5-f5adb7e35526</t>
         </is>
@@ -2992,12 +3008,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>c43ca22b-0d20-4266-88fa-8466cce93741</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>73458e24-3b00-40b4-bc98-17db997a5de3</t>
         </is>
@@ -3079,12 +3095,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>af9a36ed-316f-4af4-b580-062e95df18d6</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>d358bd95-8176-4422-b682-f6e544cdb770</t>
         </is>
@@ -3166,12 +3182,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>9f0a38ad-35a7-44e8-92c6-dfde6c985ace</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>6ee036da-686e-48c4-a8b3-f575c520b7c1</t>
         </is>
@@ -3253,12 +3269,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>21b8abac-673d-4f63-8ea4-76f30d8f2458</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>0484ffb8-6170-40e5-862e-b2e4a75e5088</t>
         </is>
@@ -3340,12 +3356,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>494d0c6e-f3cb-4e15-bb22-bfbe22178fb0</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>32ecf904-b136-4b13-9c64-272262e5cb6c</t>
         </is>
@@ -3427,12 +3443,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>f44f31d9-2243-4cb0-b026-0bf6e54e6ce2</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>1a50f116-8558-47a7-9406-05b4c32218d3</t>
         </is>
@@ -3514,12 +3530,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>3df93711-843f-4b92-8603-2cd74965293d</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>30095be2-2b8b-40d6-a034-79e0f76cf0fb</t>
         </is>
@@ -3601,12 +3617,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>74298efc-8cd2-40b0-851c-907bc5877cb3</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>ba54a51f-ff90-4a01-82c7-8b04eb6672cb</t>
         </is>
@@ -3688,12 +3704,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>75e62c9c-68ed-48aa-992b-33fff2dc82d2</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>7ae6d243-acde-4c58-94fe-0eb235d2833d</t>
         </is>
@@ -3825,20 +3841,25 @@
       </c>
       <c r="X46" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y46" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y46" s="1" t="inlineStr">
+      <c r="Z46" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z46" s="1" t="inlineStr">
+      <c r="AA46" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA46" s="1" t="inlineStr">
+      <c r="AB46" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3930,12 +3951,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>669cb388-350d-4427-ac35-af60f0c29c11</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>045eead8-67d6-43d4-b853-5e5cadabd6d4</t>
         </is>
@@ -4022,17 +4043,17 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>a69b1dd2-d4ba-4f1c-b392-c1ae5b5b81c2</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>0dad6580-c18b-4b95-9d2c-2d0149424352</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>669cb388-350d-4427-ac35-af60f0c29c11</t>
         </is>
@@ -4124,17 +4145,17 @@
           <t>The White Heron cancels the Knee.</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>9688517c-2ed0-4fed-a34d-76e10b004eeb</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>8c731331-988c-4d9c-8596-7d5f066733b9</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>a69b1dd2-d4ba-4f1c-b392-c1ae5b5b81c2</t>
         </is>
@@ -4221,17 +4242,17 @@
           <t>hhmshhm</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>99016883-22f7-46e2-a6b8-ce5a61a0d420</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>cf9f2947-d848-4d7e-9c05-30092d50f675</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>9688517c-2ed0-4fed-a34d-76e10b004eeb</t>
         </is>
@@ -4323,17 +4344,17 @@
           <t>JG BS</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>7fc69d38-3ebd-4e97-9de3-fd5c4f4bea32</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>edf632be-2d1a-4d2c-9c97-04b569692098</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>9688517c-2ed0-4fed-a34d-76e10b004eeb</t>
         </is>
@@ -4425,12 +4446,12 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>ad864b4e-ead0-4496-91b5-f34a0004c607</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>701beb9c-1194-4ce6-b668-69ef292b6c69</t>
         </is>
@@ -4522,12 +4543,12 @@
           <t>hhh</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>a208103e-6af6-44d4-bd61-39c05b0478e5</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>af2f7818-41dc-43c6-8734-be6aec1c5b57</t>
         </is>
@@ -4536,22 +4557,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WS+1,2 - [~5]</t>
+          <t>WS+1,2 -</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WS+1,2 - [~5]</t>
+          <t>WS+1,2 -</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Twin Pistons - [Tag]</t>
+          <t>Twin Pistons -</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twin Pistons - [Tag]</t>
+          <t>Twin Pistons -</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4626,10 +4647,15 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>92abbd98-841a-40a6-9f2c-f893c21e340e</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>9cbbe317-54bf-4ee0-96d3-1790b5bd954c</t>
         </is>
@@ -4731,12 +4757,12 @@
           <t>Damage if the 1st hit is 12 if you don't execute the 2nd hit.</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>55290405-aecb-431d-8776-2711101b6b52</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>05b3cfcc-36dd-4b14-b695-6372cb45c631</t>
         </is>
@@ -4833,12 +4859,12 @@
           <t>On a clean hit damage will be 43 and the opponent is knocked down.</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>0319b4a5-9818-44bd-ba56-ebe692edf5e4</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>369503a8-a513-463a-b657-8a6fd30dc8b3</t>
         </is>
@@ -4925,17 +4951,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>31143497-6374-4945-ab57-794c3f53f5f0</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>264f8dcc-2d0a-401a-b94f-2acf6b20d9b3</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>0319b4a5-9818-44bd-ba56-ebe692edf5e4</t>
         </is>
@@ -5027,17 +5053,17 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>f722eb0e-9ea9-4640-8c8f-071535c4f894</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>2ccd3675-3eda-453b-872c-3ca8e7e7a7cc</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>0319b4a5-9818-44bd-ba56-ebe692edf5e4</t>
         </is>
@@ -5129,12 +5155,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>ae24f3fa-b66c-4c48-af36-424ab0f494d8</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>6357306f-64d7-44d5-b5e5-33a2957ce50a</t>
         </is>
@@ -5231,12 +5257,12 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>1b2534aa-8b82-4a86-ab3f-f25c4c4483a3</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>b343de68-5a6c-42ae-adc2-f3dc237905b6</t>
         </is>
@@ -5308,17 +5334,17 @@
           <t>m-</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>f94365bb-dcec-423a-a128-69b3dd5acbe8</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>1b2534aa-8b82-4a86-ab3f-f25c4c4483a3</t>
         </is>
@@ -5415,17 +5441,17 @@
           <t>On a clean hit damage will be 43 and the opponent is knocked down.</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>32805c14-f4cd-468e-bce2-3f99b661f511</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>f887b34b-5bf7-4ba1-8429-5f9cced91971</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
@@ -5512,17 +5538,17 @@
           <t>m-mm</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>ec808cdb-142e-457c-9e63-ee7cb1ab1e08</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>9646c1c3-2ab3-4203-a85c-870c0905b64b</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>32805c14-f4cd-468e-bce2-3f99b661f511</t>
         </is>
@@ -5609,17 +5635,17 @@
           <t>m-mL</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>db554e15-9dd5-40bb-a681-78c2cb6b50bc</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>d75d590a-9e2b-4b0e-841d-694baca41bfe</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>32805c14-f4cd-468e-bce2-3f99b661f511</t>
         </is>
@@ -5628,22 +5654,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>–– 2 [~5]</t>
+          <t>–– 2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>b+1~df,2 [~5]</t>
+          <t>b+1~df,2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>–– Wind Godfist [Tag]</t>
+          <t>–– Wind Godfist</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Parting Wave – Crouch Dash – Wind Godfist [Tag]</t>
+          <t>Parting Wave – Crouch Dash – Wind Godfist</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5723,15 +5749,20 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
           <t>21a7ca65-38cc-4c3c-9201-26510decb0b1</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>808ca106-be9c-4427-b53b-ad72b7191a45</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
@@ -5833,17 +5864,17 @@
           <t>Delayed Hell Sweep will do 15 damage.</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>924c9b14-97be-4ca5-ba8f-9bba0c6b200c</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>e19b04f7-fa46-45c6-ad45-082db6cd6f72</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>1ac36d3f-3503-4dbc-8663-90c00452f8f0</t>
         </is>
@@ -5930,17 +5961,17 @@
           <t>m-Lm</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>19f58a55-6e04-4800-92e8-2a9f9634e1b3</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>304ed77b-d5e6-4f96-8310-28f837a8a331</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>924c9b14-97be-4ca5-ba8f-9bba0c6b200c</t>
         </is>
@@ -6037,12 +6068,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>aa1f7bcf-d6c5-4a66-92db-b709d925fed9</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>66647df7-5707-4ccd-a047-75919930e4fd</t>
         </is>
@@ -6129,17 +6160,17 @@
           <t>hhmm</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>be6db272-1872-48d5-9c9c-0d0d059d5ada</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>e899180b-907f-47fe-b4c1-51f3ed45d0ca</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>aa1f7bcf-d6c5-4a66-92db-b709d925fed9</t>
         </is>
@@ -6226,17 +6257,17 @@
           <t>hhmm</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>b8dda983-35af-47e1-81b8-7d28611a9ca4</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>0b62fbc4-6648-4c9b-9255-56bc93cd8050</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>aa1f7bcf-d6c5-4a66-92db-b709d925fed9</t>
         </is>
@@ -6328,12 +6359,12 @@
           <t>shh</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>7727ab03-4896-4e56-a0cc-ef259d5609a1</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>ceb1087f-ef43-4ee6-9c5f-ca58d0717282</t>
         </is>
@@ -6420,17 +6451,17 @@
           <t>shhm</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>4f2d088d-12f5-4b05-ba54-bb7c40204ad8</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>9cf0dfcc-e927-4113-85ac-5bb883586652</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>7727ab03-4896-4e56-a0cc-ef259d5609a1</t>
         </is>
@@ -6522,17 +6553,17 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>16c7aa83-e339-43c8-a2f8-aa7ab167725f</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>31c4aaa9-a4ab-4af5-8d94-4e189b09df6e</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>7727ab03-4896-4e56-a0cc-ef259d5609a1</t>
         </is>
@@ -6629,12 +6660,12 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>9e1f3903-15f1-4a2c-a2a8-d83b2d52b8b1</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>eee6d2a5-65ff-4b6d-ab74-72e968413ef6</t>
         </is>
@@ -6726,12 +6757,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>a52b1077-3f2d-44b5-8bfd-7abb752d6c16</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>f8fb3ca9-b75e-453e-b832-e17fa6dc20fa</t>
         </is>
@@ -6823,12 +6854,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>313d53a0-01cb-491d-ba60-b1ba2ab0d0db</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>7db7cd03-9175-41af-beff-21dbec65f76d</t>
         </is>
@@ -6925,12 +6956,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>e69bbfdd-c4a0-4d54-ac12-9a59e92ea818</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>b1da4954-3ba2-4089-8137-ba663ba7033d</t>
         </is>
@@ -7027,12 +7058,12 @@
           <t>GB KS</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>fdc31ca3-48a9-4efa-8ccb-d201525fa498</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>9ec0bb5c-013b-4ea4-94e6-2fd536123703</t>
         </is>
@@ -7119,17 +7150,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>f0a61edd-4f44-4b68-816e-20604e9decfe</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>3726ac53-edb0-49f1-8d18-aeea5b883c73</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>fdc31ca3-48a9-4efa-8ccb-d201525fa498</t>
         </is>
@@ -7138,22 +7169,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WS+2 - [~5]</t>
+          <t>WS+2 -</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WS+2 - [~5]</t>
+          <t>WS+2 -</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Uppercut - [Tag]</t>
+          <t>Uppercut -</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Uppercut - [Tag]</t>
+          <t>Uppercut -</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7223,10 +7254,15 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
           <t>b5c3b733-3b05-4b65-8aa7-137cfd48bec5</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>9f12c745-f5fc-4502-9b1d-ed6949b920ec</t>
         </is>
@@ -7318,12 +7354,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>65a0ea49-07a7-499f-9581-0c1333c51a47</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>c69d843f-ccc5-451c-9327-bd6d7462dee6</t>
         </is>
@@ -7332,22 +7368,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SS+2 - [~5]</t>
+          <t>SS+2 -</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SS+2 - [~5]</t>
+          <t>SS+2 -</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tooth Fairy - [Tag]</t>
+          <t>Tooth Fairy -</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tooth Fairy - [Tag]</t>
+          <t>Tooth Fairy -</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7422,10 +7458,15 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
           <t>c6e4830e-a3cb-460d-9b03-0c4fe13b1861</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>d9fd1d99-6c7f-4cee-b7c4-8e43b8eadb3c</t>
         </is>
@@ -7434,22 +7475,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>f,N,d,df+2 - [~5]</t>
+          <t>f,N,d,df+2 -</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>f,N,d,df+2 - [~5]</t>
+          <t>f,N,d,df+2 -</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wind Godfist - [Tag]</t>
+          <t>Wind Godfist -</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wind Godfist - [Tag]</t>
+          <t>Wind Godfist -</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7529,10 +7570,15 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
           <t>770ef824-eb8e-49ff-828c-c73385a322d8</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>aa597aea-56c0-4bb7-bbef-181b56d3f130</t>
         </is>
@@ -7629,12 +7675,12 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>f74f0a65-e789-461e-8435-0b5e83600664</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>7825cdfc-53e7-41bd-b8a6-a855b81fa910</t>
         </is>
@@ -7643,22 +7689,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>f~N,d~df+2 - [~5]</t>
+          <t>f~N,d~df+2 -</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>f~N,d~df+2 - [~5]</t>
+          <t>f~N,d~df+2 -</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Electric Wind Godfist - [Tag]</t>
+          <t>Electric Wind Godfist -</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Electric Wind Godfist - [Tag]</t>
+          <t>Electric Wind Godfist -</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7738,10 +7784,15 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
           <t>ae1401a6-1714-44f2-8821-a0baa135dd79</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>be1a74c2-8f87-4609-afa7-dc9184b38436</t>
         </is>
@@ -7798,12 +7849,12 @@
           <t>DSc</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>fbf6020b-c701-4c61-a21a-2a9cf91994c2</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>fcfe6800-c051-4c60-8ebb-1dba925779f6</t>
         </is>
@@ -7905,12 +7956,12 @@
           <t>The stun occurs on the 2nd hit.</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>df4c3b3f-35a0-418c-935b-6a3cc714e622</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>9fecf366-a307-49eb-b28d-41f90024c192</t>
         </is>
@@ -7919,22 +7970,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>b,f+2&lt;1&lt;d+2 - [~5]</t>
+          <t>b,f+2&lt;1&lt;d+2 -</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>b,f+2&lt;1&lt;d+2 - [~5]</t>
+          <t>b,f+2&lt;1&lt;d+2 -</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Laser Scraper - [Tag]</t>
+          <t>Laser Scraper -</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Laser Scraper - [Tag]</t>
+          <t>Laser Scraper -</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8014,10 +8065,15 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>99c069f9-a4c3-4982-9d97-b5409dcd7cdd</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>d9765e4f-d363-4d86-86d8-c6c9b1d7a870</t>
         </is>
@@ -8114,12 +8170,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>a8af5950-edb9-4682-8d72-18378d0708d5</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>ee7f03ae-efff-42b0-a39b-b15f044b9a86</t>
         </is>
@@ -8211,12 +8267,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>a39c346e-9b6b-4131-8daa-b88b7fd25259</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>45d143f4-13b8-4eba-b8d0-a1a9a7e5b353</t>
         </is>
@@ -8313,12 +8369,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>64585d4f-ce41-42ba-9698-a3f8a88bf1d2</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>b4f6d915-9ca9-46fc-9157-4f0c997c79b8</t>
         </is>
@@ -8420,12 +8476,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>68cbc93a-0539-4f0e-81a6-3d4c45f0f829</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>a5bafe53-552b-49fd-90d0-4e83535abad9</t>
         </is>
@@ -8522,12 +8578,12 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>d5bd8f24-b46e-46c4-b044-d58438dfe3be</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>16787ad0-a22f-4167-85d5-d76c2ab1d016</t>
         </is>
@@ -8619,12 +8675,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>e3754cba-9f84-439e-8d30-ff9150d53ae3</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>17fec100-5d47-4817-89b9-184f74f89113</t>
         </is>
@@ -8721,12 +8777,12 @@
           <t>GB CSc</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>336298c6-0c3d-47f2-82a6-9d3a8b11ce2f</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>2d11dbdb-6a2e-489b-8c19-610c7de983e7</t>
         </is>
@@ -8818,12 +8874,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>ce76da72-2fd7-4d3c-a276-7a94b91944c4</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>f5fccfb6-5c33-48df-b67a-104ac4f0d9d5</t>
         </is>
@@ -8915,12 +8971,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>8db9280b-917a-46e5-aecf-fd7b683e33f0</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>0cc341f1-ca25-4619-8c1d-896ddd3085d2</t>
         </is>
@@ -9012,12 +9068,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>98df75bc-7a72-4ee3-ba14-2f7d466cb661</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>79bc66dd-9efd-4eb4-b666-918266263133</t>
         </is>
@@ -9119,12 +9175,12 @@
           <t>Delayed Hell Sweep will do 15 damage.</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>e9f6cff8-a95f-4d33-91f6-0ad21241001f</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>a778e855-8b54-4252-8729-b450b91db2ec</t>
         </is>
@@ -9211,17 +9267,17 @@
           <t>Lm</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>e02a3aad-2719-4b53-836a-cc355339921a</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>6f33dead-8e18-42ea-b5e4-dbd066054ad2</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>e9f6cff8-a95f-4d33-91f6-0ad21241001f</t>
         </is>
@@ -9318,12 +9374,12 @@
           <t>BS</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>c155f9cf-5c28-4c82-8db4-9ef29f80ef8e</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>05d296f9-b06e-46a2-afc5-bf6c7ce9e184</t>
         </is>
@@ -9410,12 +9466,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>198d48e3-fb8e-4387-b90f-d12b4dbd87ad</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>93cae035-e68a-4565-bb24-bf140795eb5f</t>
         </is>
@@ -9472,12 +9528,12 @@
           <t>Repels all attacks.</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>8d2d7bbe-a352-4a55-a376-1a80e099ac3d</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>ecf1eb8f-c712-4f7d-a0b4-df4bc94c264e</t>
         </is>
@@ -9534,12 +9590,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>accd5398-5cb2-461a-897c-7c36276e215c</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>69d1950c-de10-4cd7-8ef5-c0608de1b2e9</t>
         </is>
@@ -9596,12 +9652,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>be9e9c82-db19-4656-b369-46a4f2a6b4fb</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>8a139512-feec-457f-97a8-dfc723fa9538</t>
         </is>
@@ -9733,20 +9789,25 @@
       </c>
       <c r="X108" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y108" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y108" s="1" t="inlineStr">
+      <c r="Z108" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z108" s="1" t="inlineStr">
+      <c r="AA108" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA108" s="1" t="inlineStr">
+      <c r="AB108" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9798,12 +9859,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>f465515c-92ff-4acc-94d8-8ab298d28cf7</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>8a0820ab-b687-470f-be5d-e7b334af9191</t>
         </is>
@@ -9860,17 +9921,17 @@
           <t>Execute the command during the Lightning Force animation. The Possession will be activated after the Lightning Force.</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>3acf8755-bc41-435d-886b-79abd35a7116</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>ed31fefd-0c5e-4f07-baea-6f6e17e9adde</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>f465515c-92ff-4acc-94d8-8ab298d28cf7</t>
         </is>
@@ -9927,17 +9988,17 @@
           <t>A fast command input will cancel the Lightning Force and the Devil Jin Possession is immediately activated.</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>30111b05-70f9-4da6-a877-84b3d46e3d8d</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>83ac34fc-bf9b-4860-8814-6f3e50c86102</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
+      <c r="AA111" t="inlineStr">
         <is>
           <t>f465515c-92ff-4acc-94d8-8ab298d28cf7</t>
         </is>
@@ -10004,12 +10065,12 @@
           <t>This throw is not escapable. During this throw you can see the markings on Jin's forehead and the red glowing eyes.</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>01abc1d9-351e-4d94-8b33-9a9388b698f1</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>09de3ccf-b4fc-49f9-8be1-db65112e51d6</t>
         </is>
@@ -10101,12 +10162,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>8fdb0781-ecd5-4a94-93c1-cedc0da09707</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>17ed1c1d-f298-48b7-b44e-95231ec3f47b</t>
         </is>
@@ -10203,12 +10264,12 @@
           <t>This is similar to Heihachi's Thunder Godfist, you can not do the Mid Kick or Heel Sweep extension.</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>1abc5d56-3bec-430b-9112-1326fb6f329b</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>7e8f123d-a441-4cf5-8446-b97f0a84435b</t>
         </is>
@@ -10305,12 +10366,12 @@
           <t>JG CFS</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="Y115" t="inlineStr">
         <is>
           <t>f88b7f72-befb-458e-9f09-b171b3fa9aa1</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Z115" t="inlineStr">
         <is>
           <t>2a2cf24e-7a76-4b70-a7af-29c412b7a21e</t>
         </is>
@@ -10412,12 +10473,12 @@
           <t>Causes an incredible 27 frames of Guard Break when blocked. And it hits MID! Kazuya and Jun take 13 of Guard Damage.</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>211f25e8-b8a6-4fa7-8ad9-d36535fc143d</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>2d78f4ac-401c-480c-85c6-5cf9d4ff22af</t>
         </is>
@@ -10519,12 +10580,12 @@
           <t>Is always a clean hit and will never cause Trip Stun.</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>a2b1ec57-c5bc-4b27-9cda-3cf4afbd5920</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>0bde4271-90d2-4c99-8c1b-7bd7cd6e8150</t>
         </is>
@@ -10616,17 +10677,17 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>a10a23da-aabc-4d35-9416-b7146853501d</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>bc390f24-a61c-4688-9423-3af7413b794a</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
+      <c r="AA118" t="inlineStr">
         <is>
           <t>a2b1ec57-c5bc-4b27-9cda-3cf4afbd5920</t>
         </is>
@@ -10713,17 +10774,17 @@
           <t>Lmm</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>decc2ad9-7173-4de0-8cb8-0d5e861ad0c4</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>2a0aa474-599f-4395-a7ab-a8ae63ac3aa6</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
+      <c r="AA119" t="inlineStr">
         <is>
           <t>a10a23da-aabc-4d35-9416-b7146853501d</t>
         </is>
@@ -10780,12 +10841,12 @@
           <t>This string is a true combo, once the left jab hits the rest cannot be blocked.</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>1ebe9db0-91f3-40f9-8e40-fbbd137c1ba2</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>89b1af4d-9854-4bd2-87d7-447a3c00b29b</t>
         </is>
@@ -10917,20 +10978,25 @@
       </c>
       <c r="X123" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y123" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y123" s="1" t="inlineStr">
+      <c r="Z123" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z123" s="1" t="inlineStr">
+      <c r="AA123" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA123" s="1" t="inlineStr">
+      <c r="AB123" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -11012,12 +11078,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="Y124" t="inlineStr">
         <is>
           <t>974230d5-9099-4004-8908-af433c5cb42d</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>1b5877c7-f5e4-470b-a90d-1f13e70937e5</t>
         </is>
@@ -11099,12 +11165,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>1fbc13b4-d496-4d8f-9512-7cd2ef99b777</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>5746804f-e3c7-472d-8513-1e5511c2e41c</t>
         </is>
@@ -11236,20 +11302,25 @@
       </c>
       <c r="X128" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y128" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y128" s="1" t="inlineStr">
+      <c r="Z128" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z128" s="1" t="inlineStr">
+      <c r="AA128" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA128" s="1" t="inlineStr">
+      <c r="AB128" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -11291,12 +11362,12 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
         </is>
       </c>
-      <c r="AA129" t="inlineStr">
+      <c r="AB129" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11338,12 +11409,12 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
         </is>
       </c>
-      <c r="AA130" t="inlineStr">
+      <c r="AB130" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11385,12 +11456,12 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="Z131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
         </is>
       </c>
-      <c r="AA131" t="inlineStr">
+      <c r="AB131" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11432,12 +11503,12 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="Z132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
         </is>
       </c>
-      <c r="AA132" t="inlineStr">
+      <c r="AB132" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11479,12 +11550,12 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Z133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
         </is>
       </c>
-      <c r="AA133" t="inlineStr">
+      <c r="AB133" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11526,12 +11597,12 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
         </is>
       </c>
-      <c r="AA134" t="inlineStr">
+      <c r="AB134" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11573,12 +11644,12 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
+      <c r="Z135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
         </is>
       </c>
-      <c r="AA135" t="inlineStr">
+      <c r="AB135" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11620,12 +11691,12 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
+      <c r="Z136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
         </is>
       </c>
-      <c r="AA136" t="inlineStr">
+      <c r="AB136" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11667,12 +11738,12 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
+      <c r="Z137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
         </is>
       </c>
-      <c r="AA137" t="inlineStr">
+      <c r="AB137" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11714,12 +11785,12 @@
           <t>hhmmm</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
-      <c r="AA138" t="inlineStr">
+      <c r="AB138" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/jin_step7.xlsx
+++ b/sources/jin_step7.xlsx
@@ -995,6 +995,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
@@ -1047,6 +1052,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
@@ -1104,6 +1114,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
@@ -1161,6 +1176,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
@@ -1218,6 +1238,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
@@ -1275,6 +1300,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>cda82971-a307-467e-ad05-57768181324c</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
@@ -1342,6 +1372,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
@@ -1404,6 +1439,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
@@ -1464,6 +1504,11 @@
       <c r="U16" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -11362,6 +11407,11 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
+        </is>
+      </c>
       <c r="Z129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
@@ -11409,6 +11459,11 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
+        </is>
+      </c>
       <c r="Z130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
@@ -11456,6 +11511,11 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
+        </is>
+      </c>
       <c r="Z131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
@@ -11503,6 +11563,11 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
+        </is>
+      </c>
       <c r="Z132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
@@ -11550,6 +11615,11 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
+        </is>
+      </c>
       <c r="Z133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
@@ -11597,6 +11667,11 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
+        </is>
+      </c>
       <c r="Z134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
@@ -11644,6 +11719,11 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
+        </is>
+      </c>
       <c r="Z135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
@@ -11691,6 +11771,11 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
+        </is>
+      </c>
       <c r="Z136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
@@ -11738,6 +11823,11 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
+        </is>
+      </c>
       <c r="Z137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
@@ -11783,6 +11873,11 @@
       <c r="S138" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
